--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -1026,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123255410</v>
+        <v>123255322</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1042,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577696</v>
+        <v>577711</v>
       </c>
       <c r="R5" t="n">
-        <v>7064508</v>
+        <v>7064481</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123255322</v>
+        <v>123255410</v>
       </c>
       <c r="B6" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,39 +1159,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577711</v>
+        <v>577696</v>
       </c>
       <c r="R6" t="n">
-        <v>7064481</v>
+        <v>7064508</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123255677</v>
+        <v>123255633</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577646</v>
+        <v>577622</v>
       </c>
       <c r="R3" t="n">
-        <v>7064511</v>
+        <v>7064523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,12 +892,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1026,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123255322</v>
+        <v>123255567</v>
       </c>
       <c r="B5" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577711</v>
+        <v>577623</v>
       </c>
       <c r="R5" t="n">
-        <v>7064481</v>
+        <v>7064574</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123255410</v>
+        <v>123255322</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577696</v>
+        <v>577711</v>
       </c>
       <c r="R6" t="n">
-        <v>7064508</v>
+        <v>7064481</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123255633</v>
+        <v>123255410</v>
       </c>
       <c r="B7" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,21 +1261,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577622</v>
+        <v>577696</v>
       </c>
       <c r="R7" t="n">
-        <v>7064523</v>
+        <v>7064508</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,12 +1345,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1489,10 +1479,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123255567</v>
+        <v>123255677</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,34 +1495,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577623</v>
+        <v>577646</v>
       </c>
       <c r="R9" t="n">
-        <v>7064574</v>
+        <v>7064511</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1569,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123255267</v>
+        <v>123255410</v>
       </c>
       <c r="B2" t="n">
         <v>79847</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577689</v>
+        <v>577696</v>
       </c>
       <c r="R2" t="n">
-        <v>7064464</v>
+        <v>7064508</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123255633</v>
+        <v>123255492</v>
       </c>
       <c r="B3" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577622</v>
+        <v>577675</v>
       </c>
       <c r="R3" t="n">
-        <v>7064523</v>
+        <v>7064550</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123255492</v>
+        <v>123255119</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577675</v>
+        <v>577710</v>
       </c>
       <c r="R4" t="n">
-        <v>7064550</v>
+        <v>7064401</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123255567</v>
+        <v>123255633</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1037,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577623</v>
+        <v>577622</v>
       </c>
       <c r="R5" t="n">
-        <v>7064574</v>
+        <v>7064523</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123255322</v>
+        <v>123255677</v>
       </c>
       <c r="B6" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,16 +1149,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1164,7 +1169,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1173,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577711</v>
+        <v>577646</v>
       </c>
       <c r="R6" t="n">
-        <v>7064481</v>
+        <v>7064511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,7 +1255,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123255410</v>
+        <v>123255267</v>
       </c>
       <c r="B7" t="n">
         <v>79847</v>
@@ -1285,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577696</v>
+        <v>577689</v>
       </c>
       <c r="R7" t="n">
-        <v>7064508</v>
+        <v>7064464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1340,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,22 +1360,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123255119</v>
+        <v>123255322</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>56680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,16 +1388,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1393,7 +1408,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577710</v>
+        <v>577711</v>
       </c>
       <c r="R8" t="n">
-        <v>7064401</v>
+        <v>7064481</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,12 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1477,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123255677</v>
+        <v>123255567</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,39 +1505,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577646</v>
+        <v>577623</v>
       </c>
       <c r="R9" t="n">
-        <v>7064511</v>
+        <v>7064574</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123255410</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123255492</v>
+        <v>123255567</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577675</v>
+        <v>577623</v>
       </c>
       <c r="R3" t="n">
-        <v>7064550</v>
+        <v>7064574</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123255119</v>
+        <v>123255267</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577710</v>
+        <v>577689</v>
       </c>
       <c r="R4" t="n">
-        <v>7064401</v>
+        <v>7064464</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123255633</v>
+        <v>123255677</v>
       </c>
       <c r="B5" t="n">
-        <v>90952</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577622</v>
+        <v>577646</v>
       </c>
       <c r="R5" t="n">
-        <v>7064523</v>
+        <v>7064511</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123255677</v>
+        <v>123255492</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577646</v>
+        <v>577675</v>
       </c>
       <c r="R6" t="n">
-        <v>7064511</v>
+        <v>7064550</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,22 +1238,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123255267</v>
+        <v>123255322</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>56683</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1266,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577689</v>
+        <v>577711</v>
       </c>
       <c r="R7" t="n">
-        <v>7064464</v>
+        <v>7064481</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,12 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123255322</v>
+        <v>123255633</v>
       </c>
       <c r="B8" t="n">
-        <v>56680</v>
+        <v>90955</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,39 +1383,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577711</v>
+        <v>577622</v>
       </c>
       <c r="R8" t="n">
-        <v>7064481</v>
+        <v>7064523</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123255567</v>
+        <v>123255119</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,34 +1495,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577623</v>
+        <v>577710</v>
       </c>
       <c r="R9" t="n">
-        <v>7064574</v>
+        <v>7064401</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1569,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,12 +1589,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123255410</v>
+        <v>123255119</v>
       </c>
       <c r="B2" t="n">
-        <v>79850</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577696</v>
+        <v>577710</v>
       </c>
       <c r="R2" t="n">
-        <v>7064508</v>
+        <v>7064401</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123255567</v>
+        <v>123255322</v>
       </c>
       <c r="B3" t="n">
-        <v>79850</v>
+        <v>56683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577623</v>
+        <v>577711</v>
       </c>
       <c r="R3" t="n">
-        <v>7064574</v>
+        <v>7064481</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123255267</v>
+        <v>123255410</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577689</v>
+        <v>577696</v>
       </c>
       <c r="R4" t="n">
-        <v>7064464</v>
+        <v>7064508</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123255677</v>
+        <v>123255492</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577646</v>
+        <v>577675</v>
       </c>
       <c r="R5" t="n">
-        <v>7064511</v>
+        <v>7064550</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123255492</v>
+        <v>123255267</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577675</v>
+        <v>577689</v>
       </c>
       <c r="R6" t="n">
-        <v>7064550</v>
+        <v>7064464</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123255322</v>
+        <v>123255567</v>
       </c>
       <c r="B7" t="n">
-        <v>56683</v>
+        <v>79852</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577711</v>
+        <v>577623</v>
       </c>
       <c r="R7" t="n">
-        <v>7064481</v>
+        <v>7064574</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,7 +1370,7 @@
         <v>123255633</v>
       </c>
       <c r="B8" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123255119</v>
+        <v>123255677</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577710</v>
+        <v>577646</v>
       </c>
       <c r="R9" t="n">
-        <v>7064401</v>
+        <v>7064511</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1589,12 +1589,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123255322</v>
+        <v>123255677</v>
       </c>
       <c r="B3" t="n">
-        <v>56683</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -833,7 +833,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577711</v>
+        <v>577646</v>
       </c>
       <c r="R3" t="n">
-        <v>7064481</v>
+        <v>7064511</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123255410</v>
+        <v>123255492</v>
       </c>
       <c r="B4" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,21 +935,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +959,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577696</v>
+        <v>577675</v>
       </c>
       <c r="R4" t="n">
-        <v>7064508</v>
+        <v>7064550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,22 +1019,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123255492</v>
+        <v>123255267</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577675</v>
+        <v>577689</v>
       </c>
       <c r="R5" t="n">
-        <v>7064550</v>
+        <v>7064464</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123255267</v>
+        <v>123255633</v>
       </c>
       <c r="B6" t="n">
-        <v>79852</v>
+        <v>90963</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1164,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577689</v>
+        <v>577622</v>
       </c>
       <c r="R6" t="n">
-        <v>7064464</v>
+        <v>7064523</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123255567</v>
+        <v>123255322</v>
       </c>
       <c r="B7" t="n">
-        <v>79852</v>
+        <v>56683</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1276,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577623</v>
+        <v>577711</v>
       </c>
       <c r="R7" t="n">
-        <v>7064574</v>
+        <v>7064481</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123255633</v>
+        <v>123255410</v>
       </c>
       <c r="B8" t="n">
-        <v>90957</v>
+        <v>79853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577622</v>
+        <v>577696</v>
       </c>
       <c r="R8" t="n">
-        <v>7064523</v>
+        <v>7064508</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,22 +1477,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123255677</v>
+        <v>123255567</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,39 +1505,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577646</v>
+        <v>577623</v>
       </c>
       <c r="R9" t="n">
-        <v>7064511</v>
+        <v>7064574</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123255119</v>
+        <v>123255492</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>78781</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577710</v>
+        <v>577675</v>
       </c>
       <c r="R2" t="n">
-        <v>7064401</v>
+        <v>7064550</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123255267</v>
+        <v>123255322</v>
       </c>
       <c r="B3" t="n">
-        <v>79856</v>
+        <v>56689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577689</v>
+        <v>577711</v>
       </c>
       <c r="R3" t="n">
-        <v>7064464</v>
+        <v>7064481</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123255677</v>
+        <v>123255410</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
+        <v>79862</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577646</v>
+        <v>577696</v>
       </c>
       <c r="R4" t="n">
-        <v>7064511</v>
+        <v>7064508</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123255492</v>
+        <v>123255267</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>79862</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577675</v>
+        <v>577689</v>
       </c>
       <c r="R5" t="n">
-        <v>7064550</v>
+        <v>7064464</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123255633</v>
+        <v>123255677</v>
       </c>
       <c r="B6" t="n">
-        <v>90966</v>
+        <v>57487</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577622</v>
+        <v>577646</v>
       </c>
       <c r="R6" t="n">
-        <v>7064523</v>
+        <v>7064511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123255410</v>
+        <v>123255633</v>
       </c>
       <c r="B7" t="n">
-        <v>79856</v>
+        <v>90983</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577696</v>
+        <v>577622</v>
       </c>
       <c r="R7" t="n">
-        <v>7064508</v>
+        <v>7064523</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123255322</v>
+        <v>123255119</v>
       </c>
       <c r="B8" t="n">
-        <v>56683</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,16 +1383,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1408,7 +1403,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1417,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577711</v>
+        <v>577710</v>
       </c>
       <c r="R8" t="n">
-        <v>7064481</v>
+        <v>7064401</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,12 +1477,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
         <v>123255567</v>
       </c>
       <c r="B9" t="n">
-        <v>79856</v>
+        <v>79862</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123255492</v>
+        <v>123255410</v>
       </c>
       <c r="B2" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577675</v>
+        <v>577696</v>
       </c>
       <c r="R2" t="n">
-        <v>7064550</v>
+        <v>7064508</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123255322</v>
+        <v>123255567</v>
       </c>
       <c r="B3" t="n">
-        <v>56689</v>
+        <v>79867</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577711</v>
+        <v>577623</v>
       </c>
       <c r="R3" t="n">
-        <v>7064481</v>
+        <v>7064574</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123255410</v>
+        <v>123255119</v>
       </c>
       <c r="B4" t="n">
-        <v>79862</v>
+        <v>57490</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577696</v>
+        <v>577710</v>
       </c>
       <c r="R4" t="n">
-        <v>7064508</v>
+        <v>7064401</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123255267</v>
+        <v>123255322</v>
       </c>
       <c r="B5" t="n">
-        <v>79862</v>
+        <v>56692</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577689</v>
+        <v>577711</v>
       </c>
       <c r="R5" t="n">
-        <v>7064464</v>
+        <v>7064481</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,12 +1126,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1136,7 +1141,7 @@
         <v>123255677</v>
       </c>
       <c r="B6" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1258,7 +1263,7 @@
         <v>123255633</v>
       </c>
       <c r="B7" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1367,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123255119</v>
+        <v>123255267</v>
       </c>
       <c r="B8" t="n">
-        <v>57487</v>
+        <v>79867</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,39 +1388,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577710</v>
+        <v>577689</v>
       </c>
       <c r="R8" t="n">
-        <v>7064401</v>
+        <v>7064464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123255567</v>
+        <v>123255492</v>
       </c>
       <c r="B9" t="n">
-        <v>79862</v>
+        <v>78786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,21 +1505,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577623</v>
+        <v>577675</v>
       </c>
       <c r="R9" t="n">
-        <v>7064574</v>
+        <v>7064550</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,12 +1589,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123255410</v>
+        <v>123255119</v>
       </c>
       <c r="B2" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577696</v>
+        <v>577710</v>
       </c>
       <c r="R2" t="n">
-        <v>7064508</v>
+        <v>7064401</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +785,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123255567</v>
+        <v>123255677</v>
       </c>
       <c r="B3" t="n">
-        <v>79867</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +813,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577623</v>
+        <v>577646</v>
       </c>
       <c r="R3" t="n">
-        <v>7064574</v>
+        <v>7064511</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +887,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123255119</v>
+        <v>123255410</v>
       </c>
       <c r="B4" t="n">
-        <v>57490</v>
+        <v>79869</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577710</v>
+        <v>577696</v>
       </c>
       <c r="R4" t="n">
-        <v>7064401</v>
+        <v>7064508</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +994,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +1004,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,12 +1019,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1138,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123255677</v>
+        <v>123255633</v>
       </c>
       <c r="B6" t="n">
-        <v>57490</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,39 +1164,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577646</v>
+        <v>577622</v>
       </c>
       <c r="R6" t="n">
-        <v>7064511</v>
+        <v>7064523</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1248,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123255633</v>
+        <v>123255267</v>
       </c>
       <c r="B7" t="n">
-        <v>90988</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577622</v>
+        <v>577689</v>
       </c>
       <c r="R7" t="n">
-        <v>7064523</v>
+        <v>7064464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1345,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123255267</v>
+        <v>123255492</v>
       </c>
       <c r="B8" t="n">
-        <v>79867</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,21 +1393,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577689</v>
+        <v>577675</v>
       </c>
       <c r="R8" t="n">
-        <v>7064464</v>
+        <v>7064550</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123255492</v>
+        <v>123255567</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>79869</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,21 +1505,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577675</v>
+        <v>577623</v>
       </c>
       <c r="R9" t="n">
-        <v>7064550</v>
+        <v>7064574</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,12 +1589,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123255267</v>
+        <v>123255492</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577689</v>
+        <v>577675</v>
       </c>
       <c r="R7" t="n">
-        <v>7064464</v>
+        <v>7064550</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,12 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,10 +1372,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123255492</v>
+        <v>123255267</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,21 +1388,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1417,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577675</v>
+        <v>577689</v>
       </c>
       <c r="R8" t="n">
-        <v>7064550</v>
+        <v>7064464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1457,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -797,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123255677</v>
+        <v>123255633</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,39 +813,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577646</v>
+        <v>577622</v>
       </c>
       <c r="R3" t="n">
-        <v>7064511</v>
+        <v>7064523</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,22 +897,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123255410</v>
+        <v>123255677</v>
       </c>
       <c r="B4" t="n">
-        <v>79869</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,34 +925,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577696</v>
+        <v>577646</v>
       </c>
       <c r="R4" t="n">
-        <v>7064508</v>
+        <v>7064511</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1004,7 +999,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123255322</v>
+        <v>123255267</v>
       </c>
       <c r="B5" t="n">
-        <v>56692</v>
+        <v>79869</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,39 +1047,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577711</v>
+        <v>577689</v>
       </c>
       <c r="R5" t="n">
-        <v>7064481</v>
+        <v>7064464</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1116,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,22 +1136,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123255633</v>
+        <v>123255492</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,21 +1164,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577622</v>
+        <v>577675</v>
       </c>
       <c r="R6" t="n">
-        <v>7064523</v>
+        <v>7064550</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,10 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123255492</v>
+        <v>123255322</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>56692</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1276,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577675</v>
+        <v>577711</v>
       </c>
       <c r="R7" t="n">
-        <v>7064550</v>
+        <v>7064481</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,19 +1365,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123255267</v>
+        <v>123255567</v>
       </c>
       <c r="B8" t="n">
         <v>79869</v>
@@ -1412,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577689</v>
+        <v>577623</v>
       </c>
       <c r="R8" t="n">
-        <v>7064464</v>
+        <v>7064574</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,12 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,19 +1477,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123255567</v>
+        <v>123255410</v>
       </c>
       <c r="B9" t="n">
         <v>79869</v>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577623</v>
+        <v>577696</v>
       </c>
       <c r="R9" t="n">
-        <v>7064574</v>
+        <v>7064508</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123255119</v>
+        <v>123255633</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577710</v>
+        <v>577622</v>
       </c>
       <c r="R2" t="n">
-        <v>7064401</v>
+        <v>7064523</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123255633</v>
+        <v>123255119</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577622</v>
+        <v>577710</v>
       </c>
       <c r="R3" t="n">
-        <v>7064523</v>
+        <v>7064401</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123255677</v>
+        <v>123255492</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,39 +925,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577646</v>
+        <v>577675</v>
       </c>
       <c r="R4" t="n">
-        <v>7064511</v>
+        <v>7064550</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,19 +1009,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123255267</v>
+        <v>123255410</v>
       </c>
       <c r="B5" t="n">
         <v>79869</v>
@@ -1071,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577689</v>
+        <v>577696</v>
       </c>
       <c r="R5" t="n">
-        <v>7064464</v>
+        <v>7064508</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lunglav på björk</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,22 +1121,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123255492</v>
+        <v>123255677</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,34 +1149,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577675</v>
+        <v>577646</v>
       </c>
       <c r="R6" t="n">
-        <v>7064550</v>
+        <v>7064511</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1233,7 +1223,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123255322</v>
+        <v>123255567</v>
       </c>
       <c r="B7" t="n">
-        <v>56692</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577711</v>
+        <v>577623</v>
       </c>
       <c r="R7" t="n">
-        <v>7064481</v>
+        <v>7064574</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,7 +1367,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123255567</v>
+        <v>123255267</v>
       </c>
       <c r="B8" t="n">
         <v>79869</v>
@@ -1417,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577623</v>
+        <v>577689</v>
       </c>
       <c r="R8" t="n">
-        <v>7064574</v>
+        <v>7064464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1452,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,22 +1472,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123255410</v>
+        <v>123255322</v>
       </c>
       <c r="B9" t="n">
-        <v>79869</v>
+        <v>56692</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,34 +1500,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577696</v>
+        <v>577711</v>
       </c>
       <c r="R9" t="n">
-        <v>7064508</v>
+        <v>7064481</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>123255633</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,55 +782,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123255119</v>
+        <v>123255492</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577710</v>
+        <v>577675</v>
       </c>
       <c r="R3" t="n">
-        <v>7064401</v>
+        <v>7064550</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123255492</v>
+        <v>123255267</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577675</v>
+        <v>577689</v>
       </c>
       <c r="R4" t="n">
-        <v>7064550</v>
+        <v>7064464</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +969,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lunglav på björk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,12 +1004,7 @@
         <v>123255410</v>
       </c>
       <c r="B5" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1133,15 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123255677</v>
+        <v>123255567</v>
       </c>
       <c r="B6" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,39 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>577646</v>
+        <v>577623</v>
       </c>
       <c r="R6" t="n">
-        <v>7064511</v>
+        <v>7064574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123255567</v>
+        <v>123254728</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,34 +1226,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>577623</v>
+        <v>577703</v>
       </c>
       <c r="R7" t="n">
-        <v>7064574</v>
+        <v>7064275</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1300,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,15 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123255267</v>
+        <v>123255119</v>
       </c>
       <c r="B8" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1383,34 +1343,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>577689</v>
+        <v>577710</v>
       </c>
       <c r="R8" t="n">
-        <v>7064464</v>
+        <v>7064401</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,12 +1417,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Lunglav på björk</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,15 +1449,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123255322</v>
+        <v>123255677</v>
       </c>
       <c r="B9" t="n">
-        <v>56692</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,16 +1460,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1520,7 +1480,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1529,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>577711</v>
+        <v>577646</v>
       </c>
       <c r="R9" t="n">
-        <v>7064481</v>
+        <v>7064511</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1524,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1534,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,6 +1563,230 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123254701</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>577702</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7064271</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123255322</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Erik-Petter-Abrahams, Erik-Petter-Abrahams, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>577711</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7064481</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-16</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11547-2025 artfynd.xlsx
+++ b/artfynd/A 11547-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255633</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255492</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255267</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255410</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255567</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123254728</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1446,6 +1481,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255119</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255677</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123254701</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1787,8 +1837,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123255322</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>